--- a/Decks/OwA.xlsx
+++ b/Decks/OwA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5D219D-5D41-4B9D-8697-0B54A42D7785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD9F446-2D15-4336-825A-073F250F8E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4931C485-E0F4-439B-89CD-B979CBF2676A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4931C485-E0F4-439B-89CD-B979CBF2676A}"/>
   </bookViews>
   <sheets>
     <sheet name="OWA" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -284,18 +284,12 @@
     <t>Oketra's Monument</t>
   </si>
   <si>
-    <t>Elves of Deep Shadow</t>
-  </si>
-  <si>
     <t>Illustrious Wanderglyph</t>
   </si>
   <si>
     <t>Wolverine Riders</t>
   </si>
   <si>
-    <t>Beledros Witherbloom</t>
-  </si>
-  <si>
     <t>Utilidades</t>
   </si>
   <si>
@@ -390,6 +384,9 @@
   </si>
   <si>
     <t>Shared Roots</t>
+  </si>
+  <si>
+    <t>June, Bounty Hunter</t>
   </si>
 </sst>
 </file>
@@ -830,7 +827,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B67" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1092,7 +1089,7 @@
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1118,7 +1115,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
@@ -1223,7 +1220,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" t="s">
         <v>35</v>
       </c>
       <c r="D29" t="s">
@@ -1374,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1389,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,13 +1398,13 @@
       </c>
       <c r="B41" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1509,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="D48" t="s">
         <v>46</v>
@@ -1520,14 +1517,14 @@
         <v>37</v>
       </c>
       <c r="B49" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C49&lt;&gt;D49</f>
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D49" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1539,27 +1536,26 @@
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F51" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="D51" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -1570,11 +1566,12 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D52" t="s">
-        <v>113</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -1585,10 +1582,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1600,10 +1597,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1615,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1630,25 +1627,25 @@
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="D57" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1657,13 +1654,13 @@
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D58" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1675,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D59" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1690,25 +1687,25 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="D60" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="D61" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1720,10 +1717,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="D62" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1735,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1750,25 +1747,25 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D64" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1780,10 +1777,10 @@
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1791,14 +1788,14 @@
         <v>63</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="D67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -1806,14 +1803,14 @@
         <v>63</v>
       </c>
       <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
+        <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>68</v>
+        <v>116</v>
+      </c>
+      <c r="D68" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1825,10 +1822,10 @@
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -1840,12 +1837,11 @@
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F70"/>
+        <v>69</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -1856,11 +1852,12 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D71" t="s">
-        <v>71</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -1871,12 +1868,11 @@
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D72" t="s">
-        <v>72</v>
-      </c>
-      <c r="F72"/>
+        <v>71</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -1887,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F73"/>
     </row>
@@ -1903,11 +1899,12 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>74</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -1918,12 +1915,11 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D75" t="s">
-        <v>75</v>
-      </c>
-      <c r="F75"/>
+        <v>74</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
@@ -1934,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D76" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F76"/>
     </row>
@@ -1950,11 +1946,12 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D77" t="s">
-        <v>77</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -1965,12 +1962,11 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D78" t="s">
-        <v>79</v>
-      </c>
-      <c r="F78"/>
+        <v>77</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
@@ -1978,13 +1974,13 @@
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D79" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="F79"/>
     </row>
@@ -1993,29 +1989,30 @@
         <v>63</v>
       </c>
       <c r="B80" s="5" t="b">
-        <f>C80&lt;&gt;D80</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D80" t="s">
-        <v>78</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="F80"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>63</v>
       </c>
       <c r="B81" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>C81&lt;&gt;D81</f>
+        <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2024,15 +2021,14 @@
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>84</v>
-      </c>
-      <c r="F82"/>
+        <v>82</v>
+      </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
@@ -2043,15 +2039,16 @@
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D83" t="s">
-        <v>85</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F83"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="B84" s="5" t="b">
         <f>C84&lt;&gt;D84</f>
@@ -2066,113 +2063,113 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>84</v>
+      </c>
+      <c r="B86" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="D86" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D88" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D89" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B90" s="5" t="b">
         <f>C90&lt;&gt;D90</f>
         <v>0</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>104</v>
+      <c r="C90" t="s">
+        <v>102</v>
       </c>
       <c r="D90" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
@@ -2187,137 +2184,137 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>91</v>
+      </c>
+      <c r="B93" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B93" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="D93" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D95" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D96" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D97" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>96</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="D98" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D99" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D100" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D101" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2338,7 +2335,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C101</xm:sqref>
+          <xm:sqref>C2:C21 C23:C28 C30:C89 C91:C101</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Decks/OwA.xlsx
+++ b/Decks/OwA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD9F446-2D15-4336-825A-073F250F8E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27400B15-40A6-47FD-ABB9-B259A7C4A136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4931C485-E0F4-439B-89CD-B979CBF2676A}"/>
   </bookViews>
@@ -287,9 +287,6 @@
     <t>Illustrious Wanderglyph</t>
   </si>
   <si>
-    <t>Wolverine Riders</t>
-  </si>
-  <si>
     <t>Utilidades</t>
   </si>
   <si>
@@ -387,6 +384,9 @@
   </si>
   <si>
     <t>June, Bounty Hunter</t>
+  </si>
+  <si>
+    <t>Grave Researcher // Reanimate</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1089,7 @@
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D39" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1386,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D48" t="s">
         <v>46</v>
@@ -1566,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F52" s="4"/>
     </row>
@@ -1582,10 +1582,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1660,7 +1660,7 @@
         <v>39</v>
       </c>
       <c r="D58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1702,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1807,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D68" t="s">
         <v>66</v>
@@ -1993,10 +1993,10 @@
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D80" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F80"/>
     </row>
@@ -2035,35 +2035,34 @@
         <v>63</v>
       </c>
       <c r="B83" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C83&lt;&gt;D83</f>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D83" t="s">
-        <v>83</v>
-      </c>
-      <c r="F83"/>
+        <v>67</v>
+      </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B84" s="5" t="b">
-        <f>C84&lt;&gt;D84</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D84" t="s">
-        <v>67</v>
+        <v>84</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2072,13 +2071,13 @@
       <c r="C85" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2087,13 +2086,13 @@
       <c r="C86" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2102,74 +2101,75 @@
       <c r="C87" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>88</v>
       </c>
       <c r="D88" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B89" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>89</v>
+        <f>C89&lt;&gt;D89</f>
+        <v>0</v>
+      </c>
+      <c r="C89" t="s">
+        <v>101</v>
       </c>
       <c r="D89" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f>C90&lt;&gt;D90</f>
-        <v>0</v>
-      </c>
-      <c r="C90" t="s">
-        <v>102</v>
-      </c>
-      <c r="D90" t="s">
-        <v>102</v>
-      </c>
+      <c r="D90" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F90"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>92</v>
+        <v>116</v>
+      </c>
+      <c r="D91" t="s">
+        <v>116</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
@@ -2184,137 +2184,137 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D94" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>95</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="D97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D99" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2335,7 +2335,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C21 C23:C28 C30:C89 C91:C101</xm:sqref>
+          <xm:sqref>C2:C21 C23:C28 C30:C88 C90:C101</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Decks/OwA.xlsx
+++ b/Decks/OwA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27400B15-40A6-47FD-ABB9-B259A7C4A136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17733670-7F7D-480F-989D-78BB0F5E4BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4931C485-E0F4-439B-89CD-B979CBF2676A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="116">
   <si>
     <t>Função</t>
   </si>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>Cryptolith Rite</t>
-  </si>
-  <si>
-    <t>Fyndhorn Elves</t>
   </si>
   <si>
     <t>Sakura-Tribe Elder</t>
@@ -1089,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1371,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1386,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1416,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1431,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1446,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1461,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1491,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1506,10 +1503,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1521,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1536,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1551,770 +1548,770 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="D58" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B59" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>62</v>
+      </c>
+      <c r="B66" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="D66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
         <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D78" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F79"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F80"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D81" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B83" s="5" t="b">
         <f>C83&lt;&gt;D83</f>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D83" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D88" t="s">
         <v>88</v>
-      </c>
-      <c r="D88" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" s="5" t="b">
         <f>C89&lt;&gt;D89</f>
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D89" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="D90" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F90"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D94" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>94</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="D97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D98" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D101" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/OwA.xlsx
+++ b/Decks/OwA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17733670-7F7D-480F-989D-78BB0F5E4BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E339872E-E544-4445-B2FE-51F5EE6DE272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4931C485-E0F4-439B-89CD-B979CBF2676A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="114">
   <si>
     <t>Função</t>
   </si>
@@ -113,9 +113,6 @@
     <t>Exotic Orchard</t>
   </si>
   <si>
-    <t>Mirrodin's Core</t>
-  </si>
-  <si>
     <t>High Market</t>
   </si>
   <si>
@@ -330,9 +327,6 @@
   </si>
   <si>
     <t>Living Death</t>
-  </si>
-  <si>
-    <t>Haywire Mite</t>
   </si>
   <si>
     <t>The Battle of Bywater</t>
@@ -858,10 +852,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
         <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1080,13 +1074,13 @@
       </c>
       <c r="B20" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1098,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1113,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1128,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1143,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1158,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1173,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1188,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1203,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1218,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1233,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1248,10 +1242,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1278,10 +1272,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1293,10 +1287,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1308,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1323,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1338,980 +1332,980 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" s="5" t="b">
         <f>C45&lt;&gt;D45</f>
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B49" s="5" t="b">
         <f>C49&lt;&gt;D49</f>
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="D54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B59" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="D59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="D66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
         <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D78" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F79"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D80" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F80"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D81" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B83" s="5" t="b">
         <f>C83&lt;&gt;D83</f>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>81</v>
+      </c>
+      <c r="B84" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D88" t="s">
         <v>87</v>
-      </c>
-      <c r="D88" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" s="5" t="b">
         <f>C89&lt;&gt;D89</f>
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D89" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="D90" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F90"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D91" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D94" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>93</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="D97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D99" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D100" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D101" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/OwA.xlsx
+++ b/Decks/OwA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E339872E-E544-4445-B2FE-51F5EE6DE272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70998655-A28C-45B7-82B2-A9D0190932E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4931C485-E0F4-439B-89CD-B979CBF2676A}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>Inspiring Statuary</t>
   </si>
   <si>
-    <t>The Soul Stone</t>
-  </si>
-  <si>
     <t>Brigid, Clachan's Heart</t>
   </si>
   <si>
@@ -260,9 +257,6 @@
     <t>Nemata, Primeval Warden</t>
   </si>
   <si>
-    <t>Bramble Sovereign</t>
-  </si>
-  <si>
     <t>Pitiless Plunderer</t>
   </si>
   <si>
@@ -272,9 +266,6 @@
     <t>Thalisse, Reverent Medium</t>
   </si>
   <si>
-    <t>Ogre Slumlord</t>
-  </si>
-  <si>
     <t>Oketra's Monument</t>
   </si>
   <si>
@@ -296,9 +287,6 @@
     <t>Halo Fountain</t>
   </si>
   <si>
-    <t>Angelic Renewal</t>
-  </si>
-  <si>
     <t>The Cabbage Merchant</t>
   </si>
   <si>
@@ -378,6 +366,18 @@
   </si>
   <si>
     <t>Grave Researcher // Reanimate</t>
+  </si>
+  <si>
+    <t>Marvin, Murderous Mimic</t>
+  </si>
+  <si>
+    <t>Tippy-Toe, Terrific Partner</t>
+  </si>
+  <si>
+    <t>Twilight Diviner</t>
+  </si>
+  <si>
+    <t>Eirdu, Carrier of Dawn</t>
   </si>
 </sst>
 </file>
@@ -849,10 +849,10 @@
       </c>
       <c r="B5" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,13 +1494,13 @@
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1542,770 +1542,770 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B54" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="D54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="D59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D61" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>60</v>
+      </c>
+      <c r="B66" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
         <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D73" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D75" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F76"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D77" t="s">
-        <v>74</v>
-      </c>
-      <c r="F77"/>
+        <v>73</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D78" t="s">
-        <v>75</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F78"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C79&lt;&gt;D79</f>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D79" t="s">
-        <v>77</v>
-      </c>
-      <c r="F79"/>
+        <v>74</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
-      </c>
-      <c r="F80"/>
+        <v>77</v>
+      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B81" s="5" t="b">
         <f>C81&lt;&gt;D81</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D81" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D82" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B83" s="5" t="b">
         <f>C83&lt;&gt;D83</f>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="D83" t="s">
-        <v>65</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="F83"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
+      </c>
+      <c r="D84" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C85&lt;&gt;D85</f>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F85"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>78</v>
+      </c>
+      <c r="B86" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B86" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="D86" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D87" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="D88" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B89" s="5" t="b">
         <f>C89&lt;&gt;D89</f>
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D89" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F90"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D93" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D94" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D95" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>84</v>
+      </c>
+      <c r="B96" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B96" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="D96" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D97" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D98" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D99" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>89</v>
+      </c>
+      <c r="B101" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B101" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="D101" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2326,7 +2326,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C21 C23:C28 C30:C88 C90:C101</xm:sqref>
+          <xm:sqref>C2:C21 C23:C28 C90:C101 C30:C88</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Decks/OwA.xlsx
+++ b/Decks/OwA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70998655-A28C-45B7-82B2-A9D0190932E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B8F55D-FB25-4B53-B81F-B50E11EBAE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4931C485-E0F4-439B-89CD-B979CBF2676A}"/>
   </bookViews>
@@ -263,9 +263,6 @@
     <t>Tendershoot Dryad</t>
   </si>
   <si>
-    <t>Thalisse, Reverent Medium</t>
-  </si>
-  <si>
     <t>Oketra's Monument</t>
   </si>
   <si>
@@ -371,13 +368,16 @@
     <t>Marvin, Murderous Mimic</t>
   </si>
   <si>
-    <t>Tippy-Toe, Terrific Partner</t>
-  </si>
-  <si>
     <t>Twilight Diviner</t>
   </si>
   <si>
     <t>Eirdu, Carrier of Dawn</t>
+  </si>
+  <si>
+    <t>Great Hall of the Citadel</t>
+  </si>
+  <si>
+    <t>Skullclamp</t>
   </si>
 </sst>
 </file>
@@ -818,7 +818,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B67" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B68" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1193,14 +1193,14 @@
         <v>9</v>
       </c>
       <c r="B28" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C28&lt;&gt;D28</f>
+        <v>1</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1211,7 +1211,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="s">
@@ -1226,11 +1226,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>35</v>
+      <c r="C30" t="s">
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,14 +1283,14 @@
         <v>9</v>
       </c>
       <c r="B34" s="5" t="b">
-        <f>C34&lt;&gt;D34</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1557,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F52" s="4"/>
     </row>
@@ -1573,10 +1573,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1614,14 +1614,14 @@
         <v>46</v>
       </c>
       <c r="B56" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C56&lt;&gt;D56</f>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="D56" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1633,25 +1633,25 @@
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1663,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1678,10 +1678,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1693,25 +1693,25 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="D61" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="D62" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1723,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="D63" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1738,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -1753,25 +1753,25 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D65" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D66" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -1794,14 +1794,14 @@
         <v>60</v>
       </c>
       <c r="B68" s="5" t="b">
-        <f t="shared" ref="B68:B101" si="1">C68&lt;&gt;D68</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="D68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1809,14 +1809,14 @@
         <v>60</v>
       </c>
       <c r="B69" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="B69:B101" si="1">C69&lt;&gt;D69</f>
+        <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>65</v>
+        <v>107</v>
+      </c>
+      <c r="D69" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -1828,10 +1828,10 @@
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -1843,12 +1843,11 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F71"/>
+        <v>66</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -1859,11 +1858,12 @@
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D72" t="s">
-        <v>68</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -1874,12 +1874,11 @@
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D73" t="s">
-        <v>69</v>
-      </c>
-      <c r="F73"/>
+        <v>68</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
@@ -1890,10 +1889,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F74"/>
     </row>
@@ -1903,14 +1902,15 @@
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D75" t="s">
-        <v>111</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F75"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
@@ -1952,10 +1952,10 @@
         <v>1</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F78"/>
     </row>
@@ -1983,10 +1983,10 @@
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D80" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2001,166 +2001,166 @@
         <v>64</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>77</v>
+      </c>
+      <c r="B82" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="D82" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B83" s="5" t="b">
         <f>C83&lt;&gt;D83</f>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F83"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B85" s="5" t="b">
         <f>C85&lt;&gt;D85</f>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D85" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F85"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D87" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B89" s="5" t="b">
         <f>C89&lt;&gt;D89</f>
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="D90" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F90"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D91" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B92" s="5" t="b">
         <f>C92&lt;&gt;D92</f>
@@ -2175,137 +2175,137 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D93" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D95" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D96" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>88</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="D97" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D98" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D99" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D100" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D101" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2326,7 +2326,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C21 C23:C28 C90:C101 C30:C88</xm:sqref>
+          <xm:sqref>C2:C21 C23:C29 C90:C101 C31:C88</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
